--- a/feat/migration-contenu-fhir/ig/StructureDefinition-fr-advance-directive-document.xlsx
+++ b/feat/migration-contenu-fhir/ig/StructureDefinition-fr-advance-directive-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T11:43:27+00:00</t>
+    <t>2026-07-01T12:03:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feat/migration-contenu-fhir/ig/StructureDefinition-fr-advance-directive-document.xlsx
+++ b/feat/migration-contenu-fhir/ig/StructureDefinition-fr-advance-directive-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T12:03:19+00:00</t>
+    <t>2026-07-03T07:33:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1339,7 +1339,7 @@
     <t>Typical use of this is a Document code with class = CDA.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-type-directive-anticipee-cisis|20260420150251</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-type-directive-anticipee-cisis|20260619134043</t>
   </si>
   <si>
     <t>Consent.provision.dataPeriod</t>

--- a/feat/migration-contenu-fhir/ig/StructureDefinition-fr-advance-directive-document.xlsx
+++ b/feat/migration-contenu-fhir/ig/StructureDefinition-fr-advance-directive-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-03T07:33:59+00:00</t>
+    <t>2026-07-08T09:43:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feat/migration-contenu-fhir/ig/StructureDefinition-fr-advance-directive-document.xlsx
+++ b/feat/migration-contenu-fhir/ig/StructureDefinition-fr-advance-directive-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T09:43:12+00:00</t>
+    <t>2026-07-08T10:07:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
